--- a/Files/main-bazar-panel-char.xlsx
+++ b/Files/main-bazar-panel-char.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$367</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$368</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -2147,6 +2147,9 @@
   </x:si>
   <x:si>
     <x:t>14/09/2026 to 18/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026 to 25/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -2602,7 +2605,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V367"/>
+  <x:dimension ref="A1:V368"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -27520,31 +27523,31 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H367" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="I367" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J367" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="K367" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="L367" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="M367" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="N367" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="O367" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="P367" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="Q367" s="3" t="s">
         <x:v>38</x:v>
@@ -27565,8 +27568,76 @@
         <x:v>38</x:v>
       </x:c>
     </x:row>
+    <x:row r="368" spans="1:22">
+      <x:c r="A368" s="3" t="s">
+        <x:v>710</x:v>
+      </x:c>
+      <x:c r="B368" s="3" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C368" s="3" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D368" s="3" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="E368" s="3" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F368" s="3" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G368" s="3" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="H368" s="3" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="I368" s="3" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="J368" s="3" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K368" s="3" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="L368" s="3" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="M368" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="N368" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="O368" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="P368" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="Q368" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="R368" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="S368" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="T368" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="U368" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="V368" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V367"/>
+  <x:autoFilter ref="A1:V368"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -27589,39 +27660,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>710</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>711</x:v>
+        <x:v>712</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>712</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>713</x:v>
+        <x:v>714</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>714</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>715</x:v>
+        <x:v>716</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>716</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>366</x:v>
+        <x:v>367</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>717</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -27629,10 +27700,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>718</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>709</x:v>
+        <x:v>710</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
